--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12327B25-F899-A545-9282-1E540A50F6C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E23F7E-6CD3-8B43-9A17-8288DAA871A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>Date</t>
   </si>
@@ -147,6 +147,18 @@
   </si>
   <si>
     <t>created Project Schedule and Time Log</t>
+  </si>
+  <si>
+    <t>Notion documentation board setup</t>
+  </si>
+  <si>
+    <t>Begin Project Charter</t>
+  </si>
+  <si>
+    <t>KAN-6</t>
+  </si>
+  <si>
+    <t>yek Sprint 1</t>
   </si>
 </sst>
 </file>
@@ -660,6 +672,43 @@
         <v>9</v>
       </c>
     </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2</v>

--- a/docs/project-management/time-log.xlsx
+++ b/docs/project-management/time-log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeffkrystek/Jeff/yek_flashcard/docs/project-management/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E23F7E-6CD3-8B43-9A17-8288DAA871A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5A3FE8-0073-F84B-8B39-986B321A332A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4780" yWindow="3780" windowWidth="27240" windowHeight="16180" xr2:uid="{0105DE84-9EB5-AE49-BB95-638DCEB5FCB9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>Date</t>
   </si>
@@ -83,9 +83,6 @@
     <t>watched Jira tutorials and began setup with cusomizations</t>
   </si>
   <si>
-    <t>set up Jira Spring 1 backlog</t>
-  </si>
-  <si>
     <t>Docuemtation</t>
   </si>
   <si>
@@ -159,6 +156,18 @@
   </si>
   <si>
     <t>yek Sprint 1</t>
+  </si>
+  <si>
+    <t>general Notion, Jira, and directory structure</t>
+  </si>
+  <si>
+    <t>set up Jira Sprint 1 backlog</t>
+  </si>
+  <si>
+    <t>total hours</t>
+  </si>
+  <si>
+    <t>Multiple initiation and planning documents completed</t>
   </si>
 </sst>
 </file>
@@ -649,7 +658,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -663,10 +672,10 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -680,16 +689,16 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
         <v>37</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>38</v>
-      </c>
-      <c r="F8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -703,10 +712,56 @@
         <v>7</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>46219</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15">
+        <f>SUM(B2:B13)</f>
+        <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
@@ -714,55 +769,55 @@
         <v>2</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
         <v>17</v>
-      </c>
-      <c r="B19" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
         <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
         <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" t="s">
         <v>25</v>
-      </c>
-      <c r="B23" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
         <v>27</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
@@ -770,7 +825,7 @@
         <v>11</v>
       </c>
       <c r="B25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
@@ -778,23 +833,23 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
         <v>31</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="s">
         <v>33</v>
-      </c>
-      <c r="B28" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>
